--- a/artfynd/A 34634-2024 artfynd.xlsx
+++ b/artfynd/A 34634-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>116636117</v>
       </c>
       <c r="B2" t="n">
-        <v>56191</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,42 +785,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116636107</v>
+        <v>116636113</v>
       </c>
       <c r="B3" t="n">
-        <v>56198</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -905,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116636137</v>
+        <v>116636136</v>
       </c>
       <c r="B4" t="n">
-        <v>56177</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,7 +925,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -988,12 +973,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,42 +1005,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116636114</v>
+        <v>116636107</v>
       </c>
       <c r="B5" t="n">
-        <v>56196</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1103,12 +1083,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34634-2024 artfynd.xlsx
+++ b/artfynd/A 34634-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116636117</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116636113</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116636136</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,8 +1132,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116636107</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>